--- a/budget/event-budget-template.xlsx
+++ b/budget/event-budget-template.xlsx
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="E14" s="14">
-        <f>SUMIF(Costs!B5:B18,"Green fees",Costs!D5:D18)+SUMIF(Costs!B5:B18,"Dinner/food",Costs!D5:D18)+SUMIF(Costs!B5:B18,"On-course refreshments",Costs!D5:D18)</f>
+        <f>SUMIF(Costs!B5:B18,"Green fees",Costs!D5:D18)+SUMIF(Costs!B5:B18,"Dinner/food",Costs!D5:D18)+SUMIF(Costs!B5:B18,"On-course refreshments",Costs!D5:D18)+SUMIF(Costs!B5:B18,"Range balls",Costs!D5:D18)+SUMIF(Costs!B5:B18,"Dinner soft drinks and coffee",Costs!D5:D18)</f>
         <v/>
       </c>
     </row>
